--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/3563-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/3563-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A66BDED4-260A-40CC-B596-31B0C9B0A940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{97B036AC-9FCE-45D5-9334-CE14671F4F58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{A21B60CA-B9F8-4968-9F99-0C202CA954CB}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{E26B7FEC-33CB-4A94-909E-649BD8ACD171}"/>
   </bookViews>
   <sheets>
     <sheet name="3563-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1514,28 +1514,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF272928-864C-4A02-8791-CDEF474DFDA3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{416CBE2E-DD00-4469-AD41-7F838EA68A15}">
   <dimension ref="A1:X39"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1569,7 +1569,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1605,7 +1605,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1725,7 +1725,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>3.21</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>28</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>28</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2024</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>2.02</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>28</v>
       </c>
@@ -2091,7 +2091,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>28</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="35">
         <v>2023</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>28</v>
       </c>
@@ -2311,7 +2311,7 @@
         <v>2.96</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>28</v>
       </c>
@@ -2385,7 +2385,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="37">
         <v>2022</v>
       </c>
@@ -2457,7 +2457,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>28</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>6.23</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>28</v>
       </c>
@@ -2605,7 +2605,7 @@
         <v>1.78</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="35">
         <v>2021</v>
       </c>
@@ -2677,7 +2677,7 @@
         <v>9.86</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>28</v>
       </c>
@@ -2751,7 +2751,7 @@
         <v>8.89</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>28</v>
       </c>
@@ -2825,7 +2825,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2020</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>5.86</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>28</v>
       </c>
@@ -2971,7 +2971,7 @@
         <v>4.37</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>28</v>
       </c>
@@ -3045,7 +3045,7 @@
         <v>1.49</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="35">
         <v>2019</v>
       </c>
@@ -3117,7 +3117,7 @@
         <v>4.96</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>28</v>
       </c>
@@ -3191,7 +3191,7 @@
         <v>4.96</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>28</v>
       </c>
@@ -3265,7 +3265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>2018</v>
       </c>
@@ -3337,7 +3337,7 @@
         <v>9.7799999999999994</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="35">
         <v>2017</v>
       </c>
@@ -3409,7 +3409,7 @@
         <v>4.83</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2016</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>7.37</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="35">
         <v>2015</v>
       </c>
@@ -3553,7 +3553,7 @@
         <v>9.23</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>2014</v>
       </c>
@@ -3625,7 +3625,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="35">
         <v>2013</v>
       </c>
@@ -3697,7 +3697,7 @@
         <v>9.14</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>2012</v>
       </c>
@@ -3769,7 +3769,7 @@
         <v>9.5399999999999991</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="35">
         <v>2011</v>
       </c>
@@ -3841,7 +3841,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="37">
         <v>2010</v>
       </c>
@@ -3913,7 +3913,7 @@
         <v>6.35</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="35">
         <v>2009</v>
       </c>
@@ -3985,7 +3985,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="37">
         <v>2008</v>
       </c>
@@ -4057,7 +4057,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="35">
         <v>2007</v>
       </c>
@@ -4129,7 +4129,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="37">
         <v>2006</v>
       </c>
@@ -4201,7 +4201,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="35" t="s">
         <v>59</v>
       </c>
